--- a/artfynd/A 11708-2026 artfynd.xlsx
+++ b/artfynd/A 11708-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,33 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104696794</v>
+        <v>104696788</v>
       </c>
       <c r="B2" t="n">
-        <v>105861</v>
+        <v>102558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224190</v>
+        <v>1262</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flockarun</t>
+          <t>Toppjungfrulin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centaurium erythraea var. erythraea</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Polygala comosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Schkuhr</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -711,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Simunde 400 m SV, Gtl</t>
+          <t>Lilla Simunde 428 m VSV, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701304</v>
+        <v>701253</v>
       </c>
       <c r="R2" t="n">
-        <v>6321791</v>
+        <v>6321841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca 700 ex. xkoord = 1652474, ykoord = 6321604</t>
+          <t>xkoord = 1652427, ykoord = 6321650</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +788,245 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134149646</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102635</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Toppjungfrulin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Polygala comosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schkuhr</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lilla Simunde, 428 m VSV, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>701260</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6321841</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>I-Got-0372</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2004-08-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2004-08-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Fuktmark på sandunderlag, på låga ryggar, öar av sand.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104696794</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106386</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224190</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Flockarun</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Centaurium erythraea var. erythraea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lilla Simunde 400 m SV, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>701304</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6321791</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2004-08-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2004-08-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 700 ex. xkoord = 1652474, ykoord = 6321604</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Fuktmark på sandunderlag, på låga ryggar, öar av sand.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>

--- a/artfynd/A 11708-2026 artfynd.xlsx
+++ b/artfynd/A 11708-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104696788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134149646</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,8 +1046,18 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104696794</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>